--- a/2026/PICHINCHA/Marzo/PICHINCHA-Marzo.xlsx
+++ b/2026/PICHINCHA/Marzo/PICHINCHA-Marzo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D198C-4F41-44B9-A7AF-D9617320BC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C9494E-78DF-46D5-9E31-7F56980DD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1320,6 +1320,8 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1389,8 +1391,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1836,10 +1837,10 @@
       <c r="B11" s="29"/>
       <c r="C11" s="123"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="130" t="s">
+      <c r="E11" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="130"/>
+      <c r="F11" s="132"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
@@ -1854,7 +1855,7 @@
         <v>42</v>
       </c>
       <c r="F12" s="56">
-        <v>-169799.8697724673</v>
+        <v>-94900.571369267185</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1874,7 +1875,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="125"/>
-      <c r="C14" s="153">
+      <c r="C14" s="130">
         <v>119977</v>
       </c>
       <c r="D14" s="42"/>
@@ -1883,7 +1884,7 @@
       </c>
       <c r="F14" s="58">
         <f>'prorrateo '!F10</f>
-        <v>629560.36840320006</v>
+        <v>332796.64199999999</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1893,7 +1894,7 @@
       <c r="B15" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="79">
+      <c r="C15" s="155">
         <v>42700</v>
       </c>
       <c r="D15" s="5"/>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="F15" s="58">
         <f>-(C40)</f>
-        <v>-554661.06999999995</v>
+        <v>-560168.38</v>
       </c>
       <c r="H15" t="s">
         <v>75</v>
@@ -1949,8 +1950,8 @@
         <v>71</v>
       </c>
       <c r="B19" s="125"/>
-      <c r="C19" s="117">
-        <v>24275.41</v>
+      <c r="C19" s="131">
+        <v>29782.720000000001</v>
       </c>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
@@ -1984,14 +1985,14 @@
       <c r="B22" s="127"/>
       <c r="C22" s="86">
         <f>SUM(C12:C21)</f>
-        <v>431558.31999999995</v>
+        <v>437065.63</v>
       </c>
       <c r="E22" s="59" t="s">
         <v>43</v>
       </c>
       <c r="F22" s="122">
         <f>SUM(F12:F21)</f>
-        <v>-94900.571369267185</v>
+        <v>-322272.3093692672</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2021,7 +2022,7 @@
         <v>72</v>
       </c>
       <c r="B25" s="129"/>
-      <c r="C25" s="154">
+      <c r="C25" s="131">
         <v>4519.75</v>
       </c>
       <c r="D25" s="5"/>
@@ -2041,8 +2042,8 @@
       <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="132"/>
-      <c r="B27" s="133"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="135"/>
       <c r="C27" s="117"/>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
@@ -2077,7 +2078,7 @@
       <c r="B30" s="47"/>
       <c r="C30" s="48">
         <f>+C29+C22</f>
-        <v>554661.06999999995</v>
+        <v>560168.38</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="19"/>
@@ -2155,7 +2156,7 @@
       </c>
       <c r="C40" s="52">
         <f>C30-C28</f>
-        <v>554661.06999999995</v>
+        <v>560168.38</v>
       </c>
       <c r="F40" s="6"/>
     </row>
@@ -2165,7 +2166,7 @@
       </c>
       <c r="C41" s="76">
         <f>+C30</f>
-        <v>554661.06999999995</v>
+        <v>560168.38</v>
       </c>
       <c r="F41" s="6"/>
     </row>
@@ -2176,7 +2177,7 @@
       <c r="B42" s="63"/>
       <c r="C42" s="64">
         <f>+C30+C39</f>
-        <v>554661.06999999995</v>
+        <v>560168.38</v>
       </c>
       <c r="E42" s="16"/>
     </row>
@@ -2188,22 +2189,22 @@
       <c r="E48" s="16"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="131"/>
-      <c r="C49" s="131"/>
-      <c r="D49" s="131"/>
-      <c r="E49" s="131"/>
+      <c r="B49" s="133"/>
+      <c r="C49" s="133"/>
+      <c r="D49" s="133"/>
+      <c r="E49" s="133"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="131"/>
-      <c r="C50" s="131"/>
-      <c r="D50" s="131"/>
-      <c r="E50" s="131"/>
+      <c r="B50" s="133"/>
+      <c r="C50" s="133"/>
+      <c r="D50" s="133"/>
+      <c r="E50" s="133"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="131"/>
-      <c r="C51" s="131"/>
-      <c r="D51" s="131"/>
-      <c r="E51" s="131"/>
+      <c r="B51" s="133"/>
+      <c r="C51" s="133"/>
+      <c r="D51" s="133"/>
+      <c r="E51" s="133"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="19"/>
@@ -2413,19 +2414,16 @@
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="40">
-        <v>205664.97020159999</v>
-      </c>
-      <c r="F5" s="79">
-        <f>E5</f>
-        <v>205664.97020159999</v>
-      </c>
+        <v>110932.21399999999</v>
+      </c>
+      <c r="F5" s="79"/>
       <c r="G5" s="66">
         <f>E5-F5</f>
-        <v>0</v>
+        <v>110932.21399999999</v>
       </c>
       <c r="H5" s="69">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
+        <v>4437.28856</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2440,11 +2438,11 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>110932.21399999999</v>
+        <v>226301.71655999997</v>
       </c>
       <c r="M5" s="38">
         <f>L5*4%+L5</f>
-        <v>115369.50255999999</v>
+        <v>235353.78522239998</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -2459,11 +2457,11 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="40">
-        <v>72743.475999999995</v>
-      </c>
-      <c r="F6" s="79">
+        <v>110932.21399999999</v>
+      </c>
+      <c r="F6" s="155">
         <f>E6</f>
-        <v>72743.475999999995</v>
+        <v>110932.21399999999</v>
       </c>
       <c r="G6" s="66">
         <f>E6-F6</f>
@@ -2505,19 +2503,16 @@
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="40">
-        <v>205664.97020159999</v>
-      </c>
-      <c r="F7" s="79">
-        <f>E7</f>
-        <v>205664.97020159999</v>
-      </c>
+        <v>110932.21399999999</v>
+      </c>
+      <c r="F7" s="79"/>
       <c r="G7" s="66">
         <f t="shared" ref="G7:G8" si="3">E7-F7</f>
-        <v>0</v>
+        <v>110932.21399999999</v>
       </c>
       <c r="H7" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4437.28856</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2532,11 +2527,11 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>110932.21399999999</v>
+        <v>226301.71655999997</v>
       </c>
       <c r="M7" s="38">
         <f t="shared" si="2"/>
-        <v>115369.50255999999</v>
+        <v>235353.78522239998</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -2551,11 +2546,11 @@
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="40">
-        <v>72743.475999999995</v>
-      </c>
-      <c r="F8" s="79">
+        <v>110932.21399999999</v>
+      </c>
+      <c r="F8" s="155">
         <f>E8</f>
-        <v>72743.475999999995</v>
+        <v>110932.21399999999</v>
       </c>
       <c r="G8" s="66">
         <f t="shared" si="3"/>
@@ -2597,11 +2592,11 @@
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="40">
-        <v>72743.475999999995</v>
-      </c>
-      <c r="F9" s="79">
+        <v>110932.21399999999</v>
+      </c>
+      <c r="F9" s="155">
         <f>E9</f>
-        <v>72743.475999999995</v>
+        <v>110932.21399999999</v>
       </c>
       <c r="G9" s="66">
         <f>E9-F9</f>
@@ -2643,19 +2638,19 @@
       </c>
       <c r="E10" s="41">
         <f t="shared" si="4"/>
-        <v>629560.36840320006</v>
+        <v>554661.06999999995</v>
       </c>
       <c r="F10" s="41">
         <f>SUM(F5:F9)</f>
-        <v>629560.36840320006</v>
+        <v>332796.64199999999</v>
       </c>
       <c r="G10" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>221864.42799999999</v>
       </c>
       <c r="H10" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8874.5771199999999</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="4"/>
@@ -2671,78 +2666,78 @@
       </c>
       <c r="L10" s="116">
         <f t="shared" si="4"/>
-        <v>554661.06999999995</v>
+        <v>785400.07511999994</v>
       </c>
       <c r="M10" s="116">
         <f t="shared" si="4"/>
-        <v>576847.51279999991</v>
+        <v>816816.07812479977</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="134"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="134"/>
-      <c r="D11" s="134"/>
-      <c r="E11" s="134"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
+      <c r="A11" s="136"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
+      <c r="L13" s="137"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="135"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="137"/>
+      <c r="K14" s="137"/>
+      <c r="L14" s="137"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="135"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="137"/>
+      <c r="L15" s="137"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2764,60 +2759,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="87"/>
       <c r="G1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="146" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="147">
+      <c r="B2" s="147"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="149">
         <v>565</v>
       </c>
-      <c r="E2" s="148"/>
+      <c r="E2" s="150"/>
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="149" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="149" t="s">
+      <c r="A3" s="151" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="149" t="s">
+      <c r="C3" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="151" t="s">
+      <c r="D3" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="136" t="s">
+      <c r="E3" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="136" t="s">
+      <c r="F3" s="138" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="136" t="s">
+      <c r="G3" s="138" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="150"/>
-      <c r="B4" s="150"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
+      <c r="A4" s="152"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="89">
@@ -2977,11 +2972,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="138"/>
-      <c r="B12" s="139"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="140"/>
+      <c r="A12" s="140"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="141"/>
+      <c r="E12" s="142"/>
       <c r="F12" s="87"/>
       <c r="G12" s="87"/>
     </row>

--- a/2026/PICHINCHA/Marzo/PICHINCHA-Marzo.xlsx
+++ b/2026/PICHINCHA/Marzo/PICHINCHA-Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C9494E-78DF-46D5-9E31-7F56980DD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4C83A9-A069-455F-B666-DBF5FEA2BD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,15 +18,20 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
   <si>
     <t>UF</t>
   </si>
@@ -232,15 +237,9 @@
     <t>PRIMER VTO</t>
   </si>
   <si>
-    <t>METROGAS</t>
-  </si>
-  <si>
     <t>ARBA</t>
   </si>
   <si>
-    <t>FLOW - INTERNET CAMARA</t>
-  </si>
-  <si>
     <t>EDESUR</t>
   </si>
   <si>
@@ -256,9 +255,6 @@
     <t>SUBIDOS EN EN3R0</t>
   </si>
   <si>
-    <t>ARTICULOS DE LIMPIEZA</t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
@@ -269,6 +265,9 @@
   </si>
   <si>
     <t>MARZO</t>
+  </si>
+  <si>
+    <t>DOARTERO JULIO - CAMBIO DE DOS AUTOMATICOS - MATERIALES Y MANO DE OBRA</t>
   </si>
 </sst>
 </file>
@@ -281,7 +280,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,13 +389,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1105,7 +1097,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1308,8 +1300,6 @@
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1320,8 +1310,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1391,7 +1379,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1470,9 +1457,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1510,9 +1497,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1545,9 +1532,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1580,9 +1584,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1759,23 +1780,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1783,27 +1804,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1811,13 +1832,13 @@
       <c r="C7" s="67"/>
       <c r="D7" s="67"/>
       <c r="E7" s="24" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F7" s="109" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1825,31 +1846,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
-      <c r="C11" s="123"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="132" t="s">
+      <c r="E11" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="132"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="128"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>64</v>
       </c>
       <c r="B12" s="50"/>
-      <c r="C12" s="119">
-        <v>18649.38</v>
-      </c>
+      <c r="C12" s="119"/>
       <c r="D12" s="5"/>
       <c r="E12" s="55" t="s">
         <v>42</v>
@@ -1858,399 +1877,343 @@
         <v>-94900.571369267185</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="50"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="122" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="123"/>
       <c r="C13" s="119">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="121"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="124" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="130">
         <v>119977</v>
       </c>
-      <c r="D14" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="58">
+        <f>'prorrateo '!F10</f>
+        <v>337233.93055999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="79">
+        <v>42700</v>
+      </c>
+      <c r="D14" s="5"/>
       <c r="E14" s="57" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F14" s="58">
-        <f>'prorrateo '!F10</f>
-        <v>332796.64199999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="124" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="155">
-        <v>42700</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="58">
-        <f>-(C40)</f>
-        <v>-560168.38</v>
-      </c>
-      <c r="H15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="50"/>
+        <f>-(C35)</f>
+        <v>-398812.47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="122" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="123"/>
+      <c r="C15" s="117">
+        <v>29782.720000000001</v>
+      </c>
+      <c r="E15" s="57"/>
+      <c r="F15" s="58"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="123"/>
       <c r="C16" s="117">
-        <v>40547.78</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="57"/>
       <c r="F16" s="58"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="124" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="50"/>
+      <c r="B17" s="123"/>
       <c r="C17" s="117">
-        <v>93539.51</v>
-      </c>
-      <c r="D17" s="5"/>
+        <v>0</v>
+      </c>
       <c r="E17" s="57"/>
       <c r="F17" s="58"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="124" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="117">
-        <v>91869.24</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="58"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="124" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="125"/>
-      <c r="C19" s="131">
-        <v>29782.720000000001</v>
-      </c>
-      <c r="E19" s="57"/>
-      <c r="F19" s="58"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="124" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="125"/>
+      <c r="H17" s="106"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="124"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="86">
+        <f>SUM(C12:C17)</f>
+        <v>192459.72</v>
+      </c>
+      <c r="E18" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="120">
+        <f>SUM(F12:F17)</f>
+        <v>-156479.11080926721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="126" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="123"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="122" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="127"/>
       <c r="C20" s="117">
-        <v>0</v>
+        <v>71833</v>
       </c>
       <c r="D20" s="5"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="124" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="125"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="122" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="127"/>
       <c r="C21" s="117">
-        <v>0</v>
-      </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="58"/>
-      <c r="H21" s="106"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="126"/>
-      <c r="B22" s="127"/>
-      <c r="C22" s="86">
-        <f>SUM(C12:C21)</f>
-        <v>437065.63</v>
-      </c>
-      <c r="E22" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="122">
-        <f>SUM(F12:F21)</f>
-        <v>-322272.3093692672</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="128" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="125"/>
-      <c r="C23" s="111"/>
+        <v>4519.75</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="130" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="131"/>
+      <c r="C22" s="117">
+        <v>130000</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="124" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="117">
-        <v>71833</v>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="107">
+        <f>SUM(C19:C23)</f>
+        <v>206352.75</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="124" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="129"/>
-      <c r="C25" s="131">
-        <v>4519.75</v>
+      <c r="E24" s="5"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="47"/>
+      <c r="C25" s="48">
+        <f>+C24+C18</f>
+        <v>398812.47</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="129"/>
-      <c r="C26" s="117">
-        <v>46750</v>
-      </c>
-      <c r="D26" s="5"/>
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="134"/>
-      <c r="B27" s="135"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="107">
-        <f>SUM(C23:C28)</f>
-        <v>123102.75</v>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="48">
-        <f>+C29+C22</f>
-        <v>560168.38</v>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
-    </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="68" t="s">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="20"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="43"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="53"/>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="43"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="53"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="52">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="60"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="52">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="77"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="80"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="77"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="85"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="77"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="80">
+        <v>0</v>
+      </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="51"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="52">
-        <v>0</v>
-      </c>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="60"/>
-      <c r="B35" s="61"/>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="63"/>
+      <c r="C34" s="64">
+        <f>SUM(C29:C33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>54</v>
+      </c>
       <c r="C35" s="52">
-        <v>0</v>
+        <f>C25-C23</f>
+        <v>398812.47</v>
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="77"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="80"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="76">
+        <f>+C25</f>
+        <v>398812.47</v>
+      </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="85"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="77"/>
-      <c r="B38" s="83"/>
-      <c r="C38" s="80">
-        <v>0</v>
-      </c>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="63"/>
-      <c r="C39" s="64">
-        <f>SUM(C34:C38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="52">
-        <f>C30-C28</f>
-        <v>560168.38</v>
-      </c>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="76">
-        <f>+C30</f>
-        <v>560168.38</v>
-      </c>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="62" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="63"/>
-      <c r="C42" s="64">
-        <f>+C30+C39</f>
-        <v>560168.38</v>
-      </c>
-      <c r="E42" s="16"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="133"/>
-      <c r="C49" s="133"/>
-      <c r="D49" s="133"/>
-      <c r="E49" s="133"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="133"/>
-      <c r="C50" s="133"/>
-      <c r="D50" s="133"/>
-      <c r="E50" s="133"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="133"/>
-      <c r="C51" s="133"/>
-      <c r="D51" s="133"/>
-      <c r="E51" s="133"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="64">
+        <f>+C25+C34</f>
+        <v>398812.47</v>
+      </c>
+      <c r="E37" s="16"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="129"/>
+      <c r="C44" s="129"/>
+      <c r="D44" s="129"/>
+      <c r="E44" s="129"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="129"/>
+      <c r="C45" s="129"/>
+      <c r="D45" s="129"/>
+      <c r="E45" s="129"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="129"/>
+      <c r="C46" s="129"/>
+      <c r="D46" s="129"/>
+      <c r="E46" s="129"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="19"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="20"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="18"/>
       <c r="B63" s="18"/>
-      <c r="C63" s="20"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C63" s="18"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="18"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="18"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B49:E51"/>
-    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="B44:E46"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2268,25 +2231,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="104" t="s">
         <v>55</v>
       </c>
@@ -2302,12 +2265,12 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="70">
-        <v>554661.06999999995</v>
+        <v>398812.47</v>
       </c>
       <c r="L1" s="70"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MARZO</v>
@@ -2327,7 +2290,7 @@
       <c r="L2" s="112"/>
       <c r="M2" s="75"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2368,7 +2331,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2402,7 +2365,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2430,7 +2393,7 @@
       </c>
       <c r="J5" s="37">
         <f>K$1/5</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="K5" s="115">
         <f>K2*D5</f>
@@ -2438,14 +2401,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>226301.71655999997</v>
+        <v>195131.99656</v>
       </c>
       <c r="M5" s="38">
         <f>L5*4%+L5</f>
-        <v>235353.78522239998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>202937.2764224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2457,11 +2420,11 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="40">
-        <v>110932.21399999999</v>
-      </c>
-      <c r="F6" s="155">
+        <v>115369.50255999999</v>
+      </c>
+      <c r="F6" s="79">
         <f>E6</f>
-        <v>110932.21399999999</v>
+        <v>115369.50255999999</v>
       </c>
       <c r="G6" s="66">
         <f>E6-F6</f>
@@ -2476,7 +2439,7 @@
       </c>
       <c r="J6" s="37">
         <f t="shared" ref="J6:J9" si="1">K$1/5</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="K6" s="115">
         <f>K2*D6</f>
@@ -2484,14 +2447,14 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="M6" s="38">
         <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>115369.50255999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>82952.993759999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2519,7 +2482,7 @@
       </c>
       <c r="J7" s="37">
         <f t="shared" si="1"/>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="K7" s="115">
         <f>K2*D7</f>
@@ -2527,14 +2490,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>226301.71655999997</v>
+        <v>195131.99656</v>
       </c>
       <c r="M7" s="38">
         <f t="shared" si="2"/>
-        <v>235353.78522239998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>202937.2764224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2542,13 +2505,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="40">
         <v>110932.21399999999</v>
       </c>
-      <c r="F8" s="155">
+      <c r="F8" s="79">
         <f>E8</f>
         <v>110932.21399999999</v>
       </c>
@@ -2565,7 +2528,7 @@
       </c>
       <c r="J8" s="37">
         <f t="shared" si="1"/>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="K8" s="115">
         <f>K2*D8</f>
@@ -2573,14 +2536,14 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="M8" s="38">
         <f t="shared" si="2"/>
-        <v>115369.50255999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>82952.993759999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2594,7 +2557,7 @@
       <c r="E9" s="40">
         <v>110932.21399999999</v>
       </c>
-      <c r="F9" s="155">
+      <c r="F9" s="79">
         <f>E9</f>
         <v>110932.21399999999</v>
       </c>
@@ -2611,7 +2574,7 @@
       </c>
       <c r="J9" s="37">
         <f t="shared" si="1"/>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="K9" s="115">
         <f>K2*D9</f>
@@ -2619,14 +2582,14 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="M9" s="38">
         <f t="shared" si="2"/>
-        <v>115369.50255999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>82952.993759999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2638,11 +2601,11 @@
       </c>
       <c r="E10" s="41">
         <f t="shared" si="4"/>
-        <v>554661.06999999995</v>
+        <v>559098.35855999996</v>
       </c>
       <c r="F10" s="41">
         <f>SUM(F5:F9)</f>
-        <v>332796.64199999999</v>
+        <v>337233.93055999995</v>
       </c>
       <c r="G10" s="49">
         <f t="shared" si="4"/>
@@ -2658,7 +2621,7 @@
       </c>
       <c r="J10" s="45">
         <f t="shared" si="4"/>
-        <v>554661.06999999995</v>
+        <v>398812.47</v>
       </c>
       <c r="K10" s="45">
         <f t="shared" si="4"/>
@@ -2666,78 +2629,78 @@
       </c>
       <c r="L10" s="116">
         <f t="shared" si="4"/>
-        <v>785400.07511999994</v>
+        <v>629551.47511999996</v>
       </c>
       <c r="M10" s="116">
         <f t="shared" si="4"/>
-        <v>816816.07812479977</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="136"/>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>654733.5341248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="132"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
+      <c r="M11" s="132"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="137"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="137"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="137"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2753,68 +2716,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="143" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="139" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="145"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="141"/>
       <c r="F1" s="87"/>
       <c r="G1" s="87"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="146" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="142" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="149">
+      <c r="B2" s="143"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="145">
         <v>565</v>
       </c>
-      <c r="E2" s="150"/>
+      <c r="E2" s="146"/>
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="151" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="151" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="147" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="153" t="s">
+      <c r="D3" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="138" t="s">
+      <c r="E3" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="138" t="s">
+      <c r="F3" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="138" t="s">
+      <c r="G3" s="134" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="152"/>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="148"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="89">
         <v>1</v>
       </c>
@@ -2837,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="89">
         <v>2</v>
       </c>
@@ -2860,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="89">
         <v>3</v>
       </c>
@@ -2883,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="89">
         <v>4</v>
       </c>
@@ -2906,7 +2869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="89">
         <v>5</v>
       </c>
@@ -2929,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="94">
         <v>6</v>
       </c>
@@ -2952,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="99" t="s">
         <v>8</v>
       </c>
@@ -2971,12 +2934,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="140"/>
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="142"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="136"/>
+      <c r="B12" s="137"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="138"/>
       <c r="F12" s="87"/>
       <c r="G12" s="87"/>
     </row>
